--- a/01_Basic Model/02_Input Data/01_Historical/DE_Input_yearly.xlsx
+++ b/01_Basic Model/02_Input Data/01_Historical/DE_Input_yearly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Competitiveness_of_RES\01_Basic Model\02_Input Data\01_Historical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B38ECF2-EE6C-490D-A4A8-96509BCF3929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D314D4-4B84-4EAB-8913-4985E24A981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9BA085BD-A4BD-4D3B-9BBD-ABB9433EC046}"/>
+    <workbookView xWindow="38280" yWindow="45" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9BA085BD-A4BD-4D3B-9BBD-ABB9433EC046}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_conv" sheetId="1" r:id="rId1"/>
@@ -193,12 +193,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="[$-1010809]dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ &quot;DM&quot;_-;\-* #,##0.00\ &quot;DM&quot;_-;_-* &quot;-&quot;??\ &quot;DM&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.00\ _D_M_-;\-* #,##0.00\ _D_M_-;_-* &quot;-&quot;??\ _D_M_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,16 +229,461 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="72"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -242,8 +691,133 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -252,8 +826,250 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -292,16 +1108,229 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="220">
+    <cellStyle name="20 % - Akzent1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="28" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="31" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="34" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="37" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="29" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="32" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="35" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="38" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1 2" xfId="144" xr:uid="{F721B20A-756A-4CC4-B37A-5EBD5560B215}"/>
+    <cellStyle name="60 % - Akzent2 2" xfId="145" xr:uid="{56AE0CAD-0587-4EB7-9161-B7C274102ECF}"/>
+    <cellStyle name="60 % - Akzent3 2" xfId="146" xr:uid="{51673907-0BA4-4CD6-AE1E-BE59071D6E07}"/>
+    <cellStyle name="60 % - Akzent4 2" xfId="147" xr:uid="{B3749187-BB13-48AB-9EFF-7A90C8B24F41}"/>
+    <cellStyle name="60 % - Akzent5 2" xfId="148" xr:uid="{020ABED4-177D-4F66-9FBC-66CE1056C63D}"/>
+    <cellStyle name="60 % - Akzent6 2" xfId="149" xr:uid="{C9CFEA21-D235-4246-BFF9-069434C6C277}"/>
+    <cellStyle name="Akzent1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="27" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="30" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="33" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="36" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="16" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="17" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Comma 11" xfId="123" xr:uid="{2EE64446-D771-43D8-821D-E4DE51F263EB}"/>
+    <cellStyle name="Comma 11 2" xfId="197" xr:uid="{E6BB9F16-6021-431F-A119-97EABD012D58}"/>
+    <cellStyle name="Comma 2" xfId="47" xr:uid="{B55A14A6-2471-4485-8CD0-F8C7712EADFE}"/>
+    <cellStyle name="Comma 2 10" xfId="178" xr:uid="{ABECFE94-4E37-4A48-8CF2-69CD7803DB78}"/>
+    <cellStyle name="Comma 2 2" xfId="48" xr:uid="{4E54D723-DC67-4C6E-8CEF-43F272CF3FA1}"/>
+    <cellStyle name="Comma 2 2 2" xfId="179" xr:uid="{F5DF22C7-9170-4AA0-BFF3-5D96C288B847}"/>
+    <cellStyle name="Comma 2 3" xfId="49" xr:uid="{6CE969E1-8F91-4325-ABD5-800BC466BF51}"/>
+    <cellStyle name="Comma 2 3 2" xfId="50" xr:uid="{A9CFDA8F-44E6-47DE-B6C4-A5ED9859AD38}"/>
+    <cellStyle name="Comma 2 3 2 2" xfId="181" xr:uid="{5517047F-1160-4636-BDF0-5847802931EE}"/>
+    <cellStyle name="Comma 2 3 3" xfId="180" xr:uid="{8B95DB74-B85E-4C44-B4BE-3F11F10A8A49}"/>
+    <cellStyle name="Comma 2 4" xfId="51" xr:uid="{E6686E04-A082-4425-9A95-54445F82E000}"/>
+    <cellStyle name="Comma 2 4 2" xfId="182" xr:uid="{69009557-72A0-4387-9395-A77EB12FC45C}"/>
+    <cellStyle name="Comma 2 5" xfId="52" xr:uid="{119BD05C-3E5D-40DC-9493-A920100EB4CE}"/>
+    <cellStyle name="Comma 2 5 2" xfId="183" xr:uid="{23DEA357-DE29-4B78-958A-7BF53528B38B}"/>
+    <cellStyle name="Comma 2 6" xfId="53" xr:uid="{828233B0-D44C-4563-B4D8-97F06DA71C26}"/>
+    <cellStyle name="Comma 2 6 2" xfId="184" xr:uid="{CC746833-1044-4E55-ACFF-3EFF6F5C7ACC}"/>
+    <cellStyle name="Comma 2 7" xfId="54" xr:uid="{AB723BE2-EA2E-49A9-BA8C-A69EEB5CDBD6}"/>
+    <cellStyle name="Comma 2 7 2" xfId="185" xr:uid="{873C9A40-0029-4EC0-BFE2-908D4011131C}"/>
+    <cellStyle name="Comma 2 8" xfId="55" xr:uid="{BF1A1C20-6DD1-4235-9413-B8E1A202E4A5}"/>
+    <cellStyle name="Comma 2 8 2" xfId="186" xr:uid="{E762B74C-05BF-40CD-A2F7-7B8788FD0178}"/>
+    <cellStyle name="Comma 2 9" xfId="56" xr:uid="{1B907645-899E-4A03-9493-57EE9D2A8F5D}"/>
+    <cellStyle name="Comma 2 9 2" xfId="187" xr:uid="{3F95FD2F-2B39-4DCC-8F4F-6BEED8FC1728}"/>
+    <cellStyle name="Comma 3" xfId="57" xr:uid="{C1DEE2A9-964E-489A-80A6-1FAC1F625659}"/>
+    <cellStyle name="Comma 3 2" xfId="58" xr:uid="{64D25416-565E-43F9-98D3-4DE02D4C81AF}"/>
+    <cellStyle name="Comma 3 2 2" xfId="189" xr:uid="{55BBD1C6-4AA7-4A05-BFF9-EBBB32F4AD5A}"/>
+    <cellStyle name="Comma 3 3" xfId="188" xr:uid="{ADC3AA04-02C7-4F6D-958C-C1D6328C9421}"/>
+    <cellStyle name="Comma 4" xfId="59" xr:uid="{89626F95-4F72-4239-BEAD-CDA1E94565C2}"/>
+    <cellStyle name="Comma 4 2" xfId="60" xr:uid="{F5B52DC4-03D2-4BC9-96C6-5EDB639482D7}"/>
+    <cellStyle name="Comma 4 2 2" xfId="168" xr:uid="{03E6F116-FAC1-42E0-970E-822A4F36DC82}"/>
+    <cellStyle name="Comma 4 2 2 2" xfId="215" xr:uid="{8E0C8BB4-E10F-44C2-B1A2-EC737BB0432A}"/>
+    <cellStyle name="Comma 4 2 3" xfId="204" xr:uid="{82FB10F6-23CD-4A6A-A051-D45103A7DD8D}"/>
+    <cellStyle name="Comma 4 3" xfId="167" xr:uid="{AB2BC153-FF78-4D97-B2AF-45CF2E29D81E}"/>
+    <cellStyle name="Comma 4 3 2" xfId="214" xr:uid="{2A0C9F50-BDCA-4366-B13A-8EE960F1174D}"/>
+    <cellStyle name="Comma 4 4" xfId="203" xr:uid="{12BC34DC-E4CD-48E8-9B5E-E6ED0A885676}"/>
+    <cellStyle name="Comma 5" xfId="61" xr:uid="{4DB614CC-FBB8-4A56-9665-26BB328D6367}"/>
+    <cellStyle name="Comma 5 2" xfId="62" xr:uid="{B91057E7-E766-41D9-938E-3E8D429E28A7}"/>
+    <cellStyle name="Comma 5 2 2" xfId="191" xr:uid="{3B42E008-D78F-4DA6-9F99-A5B4864DBD8D}"/>
+    <cellStyle name="Comma 5 3" xfId="190" xr:uid="{48E32973-4C38-456D-8D19-3830AE507A84}"/>
+    <cellStyle name="Comma 6" xfId="63" xr:uid="{437BE27B-C12A-4B53-95D9-9C55D2F1F904}"/>
+    <cellStyle name="Comma 6 2" xfId="64" xr:uid="{CB2E3896-A2B2-4DB7-99A3-0E42871546E2}"/>
+    <cellStyle name="Comma 6 2 2" xfId="193" xr:uid="{71D97CEF-C45F-464A-87A6-FFE40FD46BC1}"/>
+    <cellStyle name="Comma 6 3" xfId="65" xr:uid="{72EDE547-11FC-4DC9-B98E-55182368BEE6}"/>
+    <cellStyle name="Comma 6 3 2" xfId="194" xr:uid="{81584AF9-FD80-4168-859F-4349DCBE2E8B}"/>
+    <cellStyle name="Comma 6 4" xfId="192" xr:uid="{7A56F846-5E4D-4B90-9145-09D3C6CCEC71}"/>
+    <cellStyle name="Comma 7" xfId="66" xr:uid="{733156E0-95CE-4245-9B08-329E663D431E}"/>
+    <cellStyle name="Comma 7 2" xfId="195" xr:uid="{DD29F182-3080-4B20-8C37-4B45826A74F4}"/>
+    <cellStyle name="Comma 8" xfId="67" xr:uid="{BD82616F-9F54-42AA-9AEA-B25976967EF0}"/>
+    <cellStyle name="Comma 8 2" xfId="196" xr:uid="{29F715BF-0C61-4F0F-A420-2C6A2BDBA982}"/>
+    <cellStyle name="Eingabe" xfId="15" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="22" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good 2" xfId="68" xr:uid="{672EB5CD-D87E-400E-BDE9-46FA85290EBE}"/>
+    <cellStyle name="Gut" xfId="13" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1 2" xfId="69" xr:uid="{26BDB23A-8FB0-43D8-B479-3B1B8A608552}"/>
+    <cellStyle name="Heading 2 2" xfId="70" xr:uid="{C43B9E13-543C-4A42-A73D-45D3A59D93C0}"/>
+    <cellStyle name="Hyperlink 2" xfId="72" xr:uid="{E5CD7A9E-84F5-455D-B3FE-0926FBCED4D5}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="130" xr:uid="{0F247F62-E4D0-4471-87FF-7014905F6F84}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="122" xr:uid="{BA483D0D-3B97-4B32-9F93-5F5687ADBC8C}"/>
+    <cellStyle name="Hyperlink 2 3 2" xfId="124" xr:uid="{49DE61CE-9F53-48A9-A012-0DF077375807}"/>
+    <cellStyle name="Hyperlink 3" xfId="73" xr:uid="{84FF4916-558F-4E9A-AA78-BC2467F3100C}"/>
     <cellStyle name="Komma 2" xfId="2" xr:uid="{AF1FA308-5BB0-4765-9052-001723E4E16E}"/>
     <cellStyle name="Komma 2 2" xfId="6" xr:uid="{546B1FA4-ED3D-4CCF-BFB1-6934F261636D}"/>
     <cellStyle name="Komma 2 2 2" xfId="7" xr:uid="{C0449768-2484-446A-AB6E-F20247C009BA}"/>
+    <cellStyle name="Komma 2 2 2 2" xfId="44" xr:uid="{18D798FA-7F1A-4F93-B20B-911650645CA2}"/>
+    <cellStyle name="Komma 2 2 2 2 2" xfId="140" xr:uid="{E93DA5EB-C224-4809-8B49-8910737CC38A}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2" xfId="172" xr:uid="{55155B22-7715-49EF-BE2B-AAB4503F3B3F}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2 2" xfId="219" xr:uid="{D31855F7-5993-4FB5-A55A-84F6032C14D9}"/>
+    <cellStyle name="Komma 2 2 2 2 2 3" xfId="208" xr:uid="{4567F919-F378-4BDD-8F21-3426CF77F4E2}"/>
+    <cellStyle name="Komma 2 2 2 2 3" xfId="166" xr:uid="{77138178-9EB4-4D3A-81C4-157BCB2ECBA7}"/>
+    <cellStyle name="Komma 2 2 2 2 3 2" xfId="213" xr:uid="{9EDF41B0-CB98-4D13-A984-1FAF809ABE1D}"/>
+    <cellStyle name="Komma 2 2 2 2 4" xfId="202" xr:uid="{E89CD00F-AC92-4DEB-8589-99A6AA237BA7}"/>
+    <cellStyle name="Komma 2 2 2 3" xfId="138" xr:uid="{42BF8BC4-4B1E-4DF1-8612-ED2FEBE6E6A3}"/>
+    <cellStyle name="Komma 2 2 2 3 2" xfId="170" xr:uid="{1471223B-943C-489A-A821-363474BC2E6A}"/>
+    <cellStyle name="Komma 2 2 2 3 2 2" xfId="217" xr:uid="{666C2D14-C525-4016-9D67-0980BED4B6F7}"/>
+    <cellStyle name="Komma 2 2 2 3 3" xfId="206" xr:uid="{4587D101-EC39-458F-8474-9851593CD292}"/>
+    <cellStyle name="Komma 2 2 2 4" xfId="164" xr:uid="{AD119CC4-5645-42BB-889F-F9BBF3756EB8}"/>
+    <cellStyle name="Komma 2 2 2 4 2" xfId="211" xr:uid="{2EFE1B98-0725-498C-B02E-BC0BF37F00EB}"/>
+    <cellStyle name="Komma 2 2 2 5" xfId="200" xr:uid="{EA6F7714-12FF-4A68-AB67-EF36F083EC87}"/>
+    <cellStyle name="Komma 2 2 3" xfId="151" xr:uid="{CCB6D173-6DFE-4129-99BA-5B5202A9EA17}"/>
+    <cellStyle name="Komma 2 2 3 2" xfId="176" xr:uid="{2039EDE6-F317-438A-A054-B6811CB65C96}"/>
+    <cellStyle name="Komma 2 2 4" xfId="42" xr:uid="{C0F8BE57-5C96-4272-8B00-824767E8F443}"/>
+    <cellStyle name="Komma 2 3" xfId="43" xr:uid="{394B8D30-591F-469C-A840-A1955DE0F4A9}"/>
+    <cellStyle name="Komma 2 3 2" xfId="139" xr:uid="{33CAB36C-0D6D-47D6-B35D-D33CABC1C1B5}"/>
+    <cellStyle name="Komma 2 3 2 2" xfId="171" xr:uid="{BA83086B-5304-4C99-B17A-F93C784831DC}"/>
+    <cellStyle name="Komma 2 3 2 2 2" xfId="218" xr:uid="{9645A9C0-98A2-47AD-BA68-5F06CDEB994B}"/>
+    <cellStyle name="Komma 2 3 2 3" xfId="207" xr:uid="{8F2E59D4-2D12-48EF-8BC3-AA1BF219864F}"/>
+    <cellStyle name="Komma 2 3 3" xfId="152" xr:uid="{71264599-37D9-42A2-B46E-330B81801A7C}"/>
+    <cellStyle name="Komma 2 3 4" xfId="165" xr:uid="{06D667C0-6728-426B-AC25-20709B016267}"/>
+    <cellStyle name="Komma 2 3 4 2" xfId="212" xr:uid="{56A8EC64-A318-4BD9-AA64-21B530AFDE11}"/>
+    <cellStyle name="Komma 2 3 5" xfId="201" xr:uid="{ADB59E9E-80D1-4B3A-8CE4-5179D9D2EE96}"/>
+    <cellStyle name="Komma 2 4" xfId="136" xr:uid="{E6AD9A83-010D-4D6A-92F6-0D9AFFA0E21A}"/>
+    <cellStyle name="Komma 2 4 2" xfId="169" xr:uid="{82165464-90A9-4045-9871-0C1AF539EC9F}"/>
+    <cellStyle name="Komma 2 4 2 2" xfId="216" xr:uid="{41C8AD0A-A5E4-4837-946B-EBFD199D4923}"/>
+    <cellStyle name="Komma 2 4 3" xfId="205" xr:uid="{D471F29D-A5F9-40BC-BD10-20CB333E1817}"/>
+    <cellStyle name="Komma 2 5" xfId="142" xr:uid="{E01D2154-374A-4019-8D25-97F64E439B96}"/>
+    <cellStyle name="Komma 2 6" xfId="163" xr:uid="{16B8A41C-9507-4D93-8E50-259F04FACD9C}"/>
+    <cellStyle name="Komma 2 6 2" xfId="210" xr:uid="{111EE43B-BC73-42FA-A41E-8FC1DCF2C0BE}"/>
+    <cellStyle name="Komma 2 7" xfId="199" xr:uid="{F03F02E0-4F46-4DFC-A8D4-4E7562005119}"/>
+    <cellStyle name="Komma 3" xfId="46" xr:uid="{CE16E985-2B7D-4689-9BD1-5B3B4D5331DB}"/>
+    <cellStyle name="Komma 3 2" xfId="150" xr:uid="{20DC581E-E80D-4312-BADB-B4BFCE33F326}"/>
+    <cellStyle name="Komma 3 2 2" xfId="177" xr:uid="{BCA46AB2-1363-43F0-951D-F5629A761F62}"/>
+    <cellStyle name="Komma 4" xfId="134" xr:uid="{31313545-D8C6-4FE2-8DC6-ED90742260E8}"/>
+    <cellStyle name="Komma 4 2" xfId="154" xr:uid="{23ABFB76-CC96-4E0C-BA12-BD431A1DAABA}"/>
+    <cellStyle name="Komma 4 2 2" xfId="198" xr:uid="{39EF3C26-4902-440A-81C5-FC7258129264}"/>
+    <cellStyle name="Komma 4 2 3" xfId="209" xr:uid="{C1A2C016-9346-4237-9360-2FED7D5B7457}"/>
+    <cellStyle name="Komma 5" xfId="156" xr:uid="{8109DDE6-CFE8-461B-A0F8-6ECA520528AC}"/>
+    <cellStyle name="Link 2" xfId="71" xr:uid="{E7F21743-A1DA-46CD-86D6-3319BC2FB170}"/>
+    <cellStyle name="Link 2 2" xfId="157" xr:uid="{154DFD16-E935-4E7F-8EC8-039B1E88462E}"/>
+    <cellStyle name="Neutral 2" xfId="143" xr:uid="{674C19A2-56CC-4212-A574-36B25528EC5B}"/>
+    <cellStyle name="Normal 10" xfId="74" xr:uid="{1FE9F05C-0A94-442D-ACB4-143EFA586288}"/>
+    <cellStyle name="Normal 11" xfId="75" xr:uid="{9EB93C82-0241-40B6-80D6-F6A802A83E24}"/>
+    <cellStyle name="Normal 12" xfId="76" xr:uid="{78F9A7FB-75F9-4AF6-A330-EFC45DAB2C13}"/>
+    <cellStyle name="Normal 13" xfId="77" xr:uid="{0FF5C48C-0D5A-4D10-9612-95EB1B149A16}"/>
+    <cellStyle name="Normal 14" xfId="78" xr:uid="{67F4D022-47B3-4E7A-84D1-0D8EAA8A5785}"/>
+    <cellStyle name="Normal 15" xfId="79" xr:uid="{DF476445-29DF-4E96-9918-DF15DFF9FDA5}"/>
+    <cellStyle name="Normal 16" xfId="80" xr:uid="{3F3CBDD3-6540-410F-897C-88D5CFC0869C}"/>
+    <cellStyle name="Normal 17" xfId="81" xr:uid="{0601133B-585F-4DAB-90D2-F5E9B9D74F76}"/>
+    <cellStyle name="Normal 17 2" xfId="82" xr:uid="{A82920BE-A1E4-4ABA-B42B-B78633443183}"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{098744FE-9844-4518-A91E-00A8F4258A86}"/>
     <cellStyle name="Normal 2 2" xfId="5" xr:uid="{FCD300CD-8039-44DF-B12D-F1531F7C3F26}"/>
+    <cellStyle name="Normal 2 2 2" xfId="84" xr:uid="{4CE2EBFC-C31B-4B26-B4A7-33D07C2D8068}"/>
+    <cellStyle name="Normal 2 3" xfId="85" xr:uid="{1C023FE2-B258-4681-A928-AA2B9F47B478}"/>
+    <cellStyle name="Normal 2 4" xfId="86" xr:uid="{898FCABC-1735-4092-9F02-F8F60386F34B}"/>
+    <cellStyle name="Normal 2 5" xfId="83" xr:uid="{8EB1542C-9108-468E-BDFF-51101272A59D}"/>
+    <cellStyle name="Normal 2 6" xfId="129" xr:uid="{35F7822F-1671-430C-A015-B436FCB18373}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{FA51F745-E432-4830-B289-30C69457E580}"/>
+    <cellStyle name="Normal 3 2" xfId="88" xr:uid="{00D83130-890E-41B0-997E-8CCE64F56E1A}"/>
+    <cellStyle name="Normal 3 2 2" xfId="89" xr:uid="{9A4F7FD2-B4E6-4B66-972A-82978A10F3BF}"/>
+    <cellStyle name="Normal 3 3" xfId="90" xr:uid="{034054A0-51C5-49DC-8A53-1AD0817F0EC7}"/>
+    <cellStyle name="Normal 3 4" xfId="91" xr:uid="{FCE7B675-D625-4644-9DE8-85DFE0346BDF}"/>
+    <cellStyle name="Normal 3 5" xfId="87" xr:uid="{CA4962D3-EDEE-4C30-B4D4-18DD50BA4972}"/>
+    <cellStyle name="Normal 4" xfId="92" xr:uid="{5F03DD89-73E5-4C19-8A29-C647C5410F28}"/>
+    <cellStyle name="Normal 4 2" xfId="93" xr:uid="{506FE9D6-92C4-49F4-BB8D-D157EE56469E}"/>
+    <cellStyle name="Normal 4 2 2" xfId="94" xr:uid="{588019F8-B378-4FFE-A283-D7077D29CE0B}"/>
+    <cellStyle name="Normal 4 3" xfId="95" xr:uid="{4EAEE568-6984-471E-A5C1-D5C67A79C4F6}"/>
+    <cellStyle name="Normal 4 3 2" xfId="127" xr:uid="{D592EFB9-8C80-43AA-83C3-C36B8C8E80A1}"/>
+    <cellStyle name="Normal 4 4" xfId="96" xr:uid="{D2260F53-184B-424A-B6BF-9416045D6C48}"/>
+    <cellStyle name="Normal 4 5" xfId="128" xr:uid="{C0D2F600-1080-4D8A-B890-4086AC86DF6A}"/>
+    <cellStyle name="Normal 5" xfId="97" xr:uid="{494D6ECF-54FA-4907-9540-30B57914A35F}"/>
+    <cellStyle name="Normal 5 2" xfId="98" xr:uid="{97C6AD2B-838E-4140-9DED-ED7323CE3DBF}"/>
+    <cellStyle name="Normal 6" xfId="99" xr:uid="{46E378B0-7A2A-4694-BE05-DB3E6877D397}"/>
+    <cellStyle name="Normal 6 2" xfId="100" xr:uid="{77F47EAB-9CE2-4468-81B7-F205F83100DC}"/>
+    <cellStyle name="Normal 7" xfId="101" xr:uid="{4CEBBC19-62FB-41D9-8E7D-A65C0FFD9EFF}"/>
+    <cellStyle name="Normal 7 2" xfId="102" xr:uid="{99654ECA-5AC3-4E12-9B6A-427A7B7F2441}"/>
+    <cellStyle name="Normal 8" xfId="103" xr:uid="{E12AEABC-9130-49EF-9E2D-3FBCF551768D}"/>
+    <cellStyle name="Normal 8 2" xfId="104" xr:uid="{75650E53-7267-4665-A8A0-73DAA3C0D99C}"/>
+    <cellStyle name="Normal 8 3" xfId="105" xr:uid="{F00AC212-906A-491B-AC16-09C6B65AF83E}"/>
+    <cellStyle name="Normal 8 4" xfId="106" xr:uid="{6E5C3DA9-3758-4904-8B9A-90F0425F08B4}"/>
+    <cellStyle name="Normal 8 5" xfId="126" xr:uid="{D99C6344-D29C-48C5-B533-413CBD99939A}"/>
+    <cellStyle name="Normal 9" xfId="107" xr:uid="{61E254C4-FB15-4EEF-A864-310B6A072C7A}"/>
+    <cellStyle name="Normal 9 2" xfId="108" xr:uid="{54134090-287C-4A1C-8401-C273BAB894F7}"/>
+    <cellStyle name="Normal 9 3" xfId="109" xr:uid="{AEBB4AE6-0D0D-48A3-949D-124F37CE01DE}"/>
+    <cellStyle name="Notiz" xfId="21" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Notiz 2" xfId="162" xr:uid="{98722DFC-3324-4A5D-848D-060A2038D2A8}"/>
+    <cellStyle name="Percent 2" xfId="111" xr:uid="{60BE7088-8FA1-4A31-A07C-77659755328D}"/>
+    <cellStyle name="Percent 3" xfId="112" xr:uid="{62FC2017-FBD7-456C-B275-64D96A377CE9}"/>
+    <cellStyle name="Percent 3 2" xfId="113" xr:uid="{F3384BEA-AE65-47A6-A6EA-EA96162F149A}"/>
+    <cellStyle name="Percent 4" xfId="114" xr:uid="{7FB1C352-171E-41DC-B138-79F5FEAC8BB5}"/>
+    <cellStyle name="Percent 4 2" xfId="115" xr:uid="{5C155ED6-D882-4C97-ABF4-776A6DA9F0DC}"/>
+    <cellStyle name="Percent 5" xfId="116" xr:uid="{96A6BCDA-76BA-473C-B59A-7C7098911727}"/>
+    <cellStyle name="Percent 5 2" xfId="117" xr:uid="{7FA4AE51-803C-45A7-B34C-F5E6B4E57761}"/>
+    <cellStyle name="Percent 6" xfId="118" xr:uid="{31D7CDCB-BBED-4358-9F81-FFD616C53E73}"/>
+    <cellStyle name="Percent 6 2" xfId="119" xr:uid="{74487407-798C-48B1-A8CD-F7D72BFF8591}"/>
+    <cellStyle name="Percent 6 3" xfId="120" xr:uid="{7C1678B0-5B41-4F57-976A-F48374698C01}"/>
+    <cellStyle name="Percent 7" xfId="121" xr:uid="{41D57D1B-7538-4D92-B77A-019BD8FBC833}"/>
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent 2" xfId="110" xr:uid="{CD8FDB42-4EDB-42E7-8D30-1C45EE7592C8}"/>
+    <cellStyle name="Prozent 3" xfId="125" xr:uid="{6A7D07F7-AD57-42F0-89A7-934DAFE65074}"/>
+    <cellStyle name="Schlecht" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="45" xr:uid="{17BB8C5F-1C02-41D3-B88C-37177BB67000}"/>
+    <cellStyle name="Standard 2 2" xfId="161" xr:uid="{35A7FB1E-6FB6-4F54-ACE2-9B7400693218}"/>
+    <cellStyle name="Standard 2 2 2" xfId="174" xr:uid="{126A4EBB-44D3-452C-8EEA-7DCC80F1A1BA}"/>
+    <cellStyle name="Standard 2 3" xfId="158" xr:uid="{ABAD88F1-F772-4CC5-9A79-24689E4BA654}"/>
+    <cellStyle name="Standard 2 4" xfId="141" xr:uid="{CA9ED3DA-37EB-4F2E-B3C4-F1253B85B84E}"/>
+    <cellStyle name="Standard 3" xfId="135" xr:uid="{3AEBD0E5-8F4D-42F3-85E9-7410F5208FA1}"/>
+    <cellStyle name="Standard 3 2" xfId="160" xr:uid="{53EBA374-9B5C-44C6-8D9A-6465FADF55D2}"/>
+    <cellStyle name="Standard 3 2 2" xfId="175" xr:uid="{5FEABFB5-E55D-4625-BC7C-70D198F9F561}"/>
+    <cellStyle name="Standard 4" xfId="137" xr:uid="{5C84D748-07C0-41BE-825F-35D4A000A6CC}"/>
+    <cellStyle name="Standard 4 2" xfId="155" xr:uid="{C849C285-3466-4C99-9F63-A5FB1EE69D7D}"/>
+    <cellStyle name="Standard 5" xfId="173" xr:uid="{CEEBDC4C-3513-4580-844D-7E71E022B6A2}"/>
+    <cellStyle name="Überschrift" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1 2" xfId="133" xr:uid="{EBCB0011-2750-45CA-8411-A3DC47ECFF50}"/>
+    <cellStyle name="Überschrift 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2 2" xfId="132" xr:uid="{38732EFD-5864-4641-812E-CD3D41689552}"/>
+    <cellStyle name="Überschrift 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3 2" xfId="131" xr:uid="{BE96937C-E919-46F1-96A8-3BF4E74D266A}"/>
+    <cellStyle name="Überschrift 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Überschrift 5" xfId="153" xr:uid="{AF711682-A6D8-4DCA-A02E-6A1667B839DA}"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="18" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Währung 2" xfId="159" xr:uid="{C38DEFDF-604C-4CDF-B56C-9BB275FA0135}"/>
+    <cellStyle name="Warnender Text" xfId="20" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="19" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1039,8 +2068,8 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1065,8 +2094,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1091,8 +2120,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1117,8 +2146,8 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1143,8 +2172,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1169,8 +2198,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
+      <c r="F10" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1195,8 +2224,8 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1221,8 +2250,8 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>0</v>
+      <c r="F12" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1247,8 +2276,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>0</v>
+      <c r="F13" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1273,8 +2302,8 @@
       <c r="E14" s="13">
         <v>0</v>
       </c>
-      <c r="F14" s="13">
-        <v>0</v>
+      <c r="F14" s="38">
+        <v>21.240000000000002</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
